--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-07-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7c3c0e925+77845]
-	GetHandleVerifier [0x0x7ff7c3c0e980+77936]
-	(No symbol) [0x0x7ff7c39c9cda]
-	(No symbol) [0x0x7ff7c3a206aa]
-	(No symbol) [0x0x7ff7c3a2095c]
-	(No symbol) [0x0x7ff7c3a73d07]
-	(No symbol) [0x0x7ff7c3a4890f]
-	(No symbol) [0x0x7ff7c3a70b07]
-	(No symbol) [0x0x7ff7c3a486a3]
-	(No symbol) [0x0x7ff7c3a11791]
-	(No symbol) [0x0x7ff7c3a12523]
-	GetHandleVerifier [0x0x7ff7c3ee683d+3059501]
-	GetHandleVerifier [0x0x7ff7c3ee0bfd+3035885]
-	GetHandleVerifier [0x0x7ff7c3f003f0+3164896]
-	GetHandleVerifier [0x0x7ff7c3c28c2e+185118]
-	GetHandleVerifier [0x0x7ff7c3c3053f+216111]
-	GetHandleVerifier [0x0x7ff7c3c172d4+113092]
-	GetHandleVerifier [0x0x7ff7c3c17489+113529]
-	GetHandleVerifier [0x0x7ff7c3bfe288+10616]
+	GetHandleVerifier [0x0x7ff7f179e925+77845]
+	GetHandleVerifier [0x0x7ff7f179e980+77936]
+	(No symbol) [0x0x7ff7f1559cda]
+	(No symbol) [0x0x7ff7f15b06aa]
+	(No symbol) [0x0x7ff7f15b095c]
+	(No symbol) [0x0x7ff7f1603d07]
+	(No symbol) [0x0x7ff7f15d890f]
+	(No symbol) [0x0x7ff7f1600b07]
+	(No symbol) [0x0x7ff7f15d86a3]
+	(No symbol) [0x0x7ff7f15a1791]
+	(No symbol) [0x0x7ff7f15a2523]
+	GetHandleVerifier [0x0x7ff7f1a7683d+3059501]
+	GetHandleVerifier [0x0x7ff7f1a70bfd+3035885]
+	GetHandleVerifier [0x0x7ff7f1a903f0+3164896]
+	GetHandleVerifier [0x0x7ff7f17b8c2e+185118]
+	GetHandleVerifier [0x0x7ff7f17c053f+216111]
+	GetHandleVerifier [0x0x7ff7f17a72d4+113092]
+	GetHandleVerifier [0x0x7ff7f17a7489+113529]
+	GetHandleVerifier [0x0x7ff7f178e288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
